--- a/DSA Tracking Sheet.xlsx
+++ b/DSA Tracking Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Structures and Algorithm\Pattern_Based_DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9516E5C-0727-48B6-BB77-02FEE87D117A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D60F0D9-1B86-494A-BAE9-A7881FE620E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{EA109011-75D6-4B4C-8940-30E2C0B9B007}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EA109011-75D6-4B4C-8940-30E2C0B9B007}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="90">
   <si>
     <t>Problem</t>
   </si>
@@ -239,106 +239,119 @@
 </t>
   </si>
   <si>
+    <t>Always remember question qualifies for Slidingwindow if subarray is contigous.
+Fixed window: size k is given. Dynamic window: expand right always, shrink left when invalid
+Window = camera frame sliding over array
+Window becomes invalid when constraint is violated e.g. map.size() &gt; 2</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Opposite End</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>If array is sorted we do not need hashmap.
+Two pointers can solve it in O(n) time and O(1) space.</t>
+  </si>
+  <si>
+    <t>Sorted array → two pointers can eliminate search space
+sum &gt; target → move right pointer
+sum &lt; target → move left pointer</t>
+  </si>
+  <si>
+    <t>Pattern Identification</t>
+  </si>
+  <si>
+    <t>Trigger : Sorted array + pair sum</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>Array|Two variables</t>
+  </si>
+  <si>
+    <t>Subarray + window size K → Fixed Sliding Window</t>
+  </si>
+  <si>
+    <t>Instead of recalculating sum of K elements every time,
+add next element and subtract element leaving window.</t>
+  </si>
+  <si>
+    <t>Queue stores indices of negative numbers inside window
+Front of queue always gives first negative
+Remove index if it leaves the window</t>
+  </si>
+  <si>
+    <t>Queue needed because we must preserve order of negative numbers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If window size is fixed,
+remove the element leaving the window.
+</t>
+  </si>
+  <si>
+    <t>Time Complexity</t>
+  </si>
+  <si>
+    <t>Space Complexity</t>
+  </si>
+  <si>
+    <t>O(n)</t>
+  </si>
+  <si>
+    <t>O(1)</t>
+  </si>
+  <si>
+    <t>Hint</t>
+  </si>
+  <si>
+    <t>HashMap tracks frequency of elements in window.
+Window valid only when map size == k.</t>
+  </si>
+  <si>
+    <t>Use long when sum may overflow int.
+Remove element from map only when frequency becomes 0.</t>
+  </si>
+  <si>
+    <t>Solved</t>
+  </si>
+  <si>
+    <t>Trigger: Modify the array in-place</t>
+  </si>
+  <si>
+    <t>Left Pointer will track 0s
+Right Pointer will Track 1s</t>
+  </si>
+  <si>
+    <t>If lesft pointer is on 0 move it
+if right pointer in on 1 move it
+else swap them</t>
+  </si>
+  <si>
     <t>1. Input is array/string/linkedlist
 2. Often sorted or sorting allowed
 3. Need to find pair/triplet/combination
 4. Problem involves comparing elements from both ends
-5. Two indices move through the array to reduce search space.</t>
-  </si>
-  <si>
-    <t>Always remember question qualifies for Slidingwindow if subarray is contigous.
-Fixed window: size k is given. Dynamic window: expand right always, shrink left when invalid
-Window = camera frame sliding over array
-Window becomes invalid when constraint is violated e.g. map.size() &gt; 2</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Opposite End</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>If array is sorted we do not need hashmap.
-Two pointers can solve it in O(n) time and O(1) space.</t>
-  </si>
-  <si>
-    <t>Sorted array → two pointers can eliminate search space
-sum &gt; target → move right pointer
-sum &lt; target → move left pointer</t>
-  </si>
-  <si>
-    <t>Pattern Identification</t>
-  </si>
-  <si>
-    <t>Trigger : Sorted array + pair sum</t>
-  </si>
-  <si>
-    <t>Easy</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>Array|Two variables</t>
-  </si>
-  <si>
-    <t>Subarray + window size K → Fixed Sliding Window</t>
-  </si>
-  <si>
-    <t>Instead of recalculating sum of K elements every time,
-add next element and subtract element leaving window.</t>
-  </si>
-  <si>
-    <t>Queue stores indices of negative numbers inside window
-Front of queue always gives first negative
-Remove index if it leaves the window</t>
-  </si>
-  <si>
-    <t>Queue needed because we must preserve order of negative numbers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If window size is fixed,
-remove the element leaving the window.
-</t>
-  </si>
-  <si>
-    <t>Time Complexity</t>
-  </si>
-  <si>
-    <t>Space Complexity</t>
-  </si>
-  <si>
-    <t>O(n)</t>
-  </si>
-  <si>
-    <t>O(1)</t>
-  </si>
-  <si>
-    <t>Hint</t>
-  </si>
-  <si>
-    <t>HashMap tracks frequency of elements in window.
-Window valid only when map size == k.</t>
-  </si>
-  <si>
-    <t>Use long when sum may overflow int.
-Remove element from map only when frequency becomes 0.</t>
-  </si>
-  <si>
-    <t>Solved</t>
+5. Two indices move through the array to reduce search space.
+6. In-place Modification is being asked</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -364,6 +377,29 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -442,7 +478,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -474,12 +510,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -490,6 +520,21 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -916,91 +961,92 @@
   <dimension ref="B5:H8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="62.5546875" customWidth="1"/>
     <col min="4" max="4" width="40.33203125" customWidth="1"/>
     <col min="5" max="5" width="22.109375" customWidth="1"/>
     <col min="6" max="6" width="28.33203125" customWidth="1"/>
     <col min="7" max="7" width="18.109375" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="13" t="s">
+    <row r="5" spans="2:8" ht="18" x14ac:dyDescent="0.35">
+      <c r="B5" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B6" s="14" t="s">
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+    </row>
+    <row r="6" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="14" t="s">
+      <c r="D6" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="142.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="171.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="19" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1014,7 +1060,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5DFE80-2C44-488B-9D8D-62ACD873F97E}">
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.21875" customWidth="1"/>
@@ -1050,7 +1096,7 @@
         <v>51</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>13</v>
@@ -1062,10 +1108,10 @@
         <v>2</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>1</v>
@@ -1091,37 +1137,37 @@
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2">
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K2" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="K2" s="15" t="s">
-        <v>82</v>
-      </c>
       <c r="L2" s="6" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -1129,23 +1175,43 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -1156,7 +1222,9 @@
       <c r="A4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
@@ -1181,7 +1249,9 @@
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
@@ -1285,10 +1355,9 @@
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="1"/>
@@ -1470,7 +1539,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1491,7 +1560,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1512,7 +1581,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1533,7 +1602,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1551,27 +1620,6 @@
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q1" xr:uid="{DF5DFE80-2C44-488B-9D8D-62ACD873F97E}"/>
@@ -1593,15 +1641,14 @@
     <hyperlink ref="A15" r:id="rId14" display="https://leetcode.com/problems/merge-sorted-array/" xr:uid="{E3FA6623-EF03-4012-92F2-24CA05E33416}"/>
     <hyperlink ref="A16" r:id="rId15" xr:uid="{08B767B9-CF56-471C-AF7A-84DA7FF9D017}"/>
     <hyperlink ref="A17" r:id="rId16" display="https://leetcode.com/problems/remove-duplicates-from-sorted-array/" xr:uid="{68CEAAD9-5603-46FC-97FE-378533FFE3B0}"/>
-    <hyperlink ref="A18" r:id="rId17" display="https://leetcode.com/problems/squares-of-a-sorted-array/" xr:uid="{A7CD254B-7F97-485E-A9B7-1FA001BD8C92}"/>
-    <hyperlink ref="A19" r:id="rId18" display="https://leetcode.com/problems/trapping-rain-water/" xr:uid="{B9927F6B-CBDA-486F-A27E-024253D5389E}"/>
-    <hyperlink ref="A20" r:id="rId19" display="https://leetcode.com/problems/move-zeroes/" xr:uid="{35A79DBB-00D5-4C74-BC90-782FC035EA7B}"/>
-    <hyperlink ref="A21" r:id="rId20" display="https://leetcode.com/problems/reverse-string/" xr:uid="{D88BB189-E81E-411F-8551-B4FAB70D208B}"/>
-    <hyperlink ref="A22" r:id="rId21" display="https://leetcode.com/problems/valid-palindrome-ii/" xr:uid="{D6F9D2FC-C252-48B2-8806-1529AC8AC8B6}"/>
+    <hyperlink ref="A18" r:id="rId17" display="https://leetcode.com/problems/trapping-rain-water/" xr:uid="{B9927F6B-CBDA-486F-A27E-024253D5389E}"/>
+    <hyperlink ref="A19" r:id="rId18" display="https://leetcode.com/problems/move-zeroes/" xr:uid="{35A79DBB-00D5-4C74-BC90-782FC035EA7B}"/>
+    <hyperlink ref="A20" r:id="rId19" display="https://leetcode.com/problems/reverse-string/" xr:uid="{D88BB189-E81E-411F-8551-B4FAB70D208B}"/>
+    <hyperlink ref="A21" r:id="rId20" display="https://leetcode.com/problems/valid-palindrome-ii/" xr:uid="{D6F9D2FC-C252-48B2-8806-1529AC8AC8B6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId22"/>
-  <drawing r:id="rId23"/>
+  <pageSetup orientation="portrait" r:id="rId21"/>
+  <drawing r:id="rId22"/>
 </worksheet>
 </file>
 
@@ -1641,7 +1688,7 @@
         <v>51</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>13</v>
@@ -1653,10 +1700,10 @@
         <v>2</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>1</v>
@@ -1678,41 +1725,41 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="14" t="s">
         <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" s="2">
         <v>60</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>52</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="J2" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K2" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="K2" s="15" t="s">
-        <v>82</v>
-      </c>
       <c r="L2" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -1721,41 +1768,41 @@
       <c r="Q2" s="7"/>
     </row>
     <row r="3" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="15" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" s="2">
         <v>120</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>52</v>
       </c>
       <c r="H3" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="I3" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>81</v>
+      <c r="J3" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
@@ -1764,41 +1811,41 @@
       <c r="Q3" s="9"/>
     </row>
     <row r="4" spans="1:17" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="16" t="s">
         <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" s="2">
         <v>120</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>52</v>
       </c>
       <c r="H4" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="I4" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>

--- a/DSA Tracking Sheet.xlsx
+++ b/DSA Tracking Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Structures and Algorithm\Pattern_Based_DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D60F0D9-1B86-494A-BAE9-A7881FE620E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185BF15C-A265-4E82-96D3-ABD93FF48AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EA109011-75D6-4B4C-8940-30E2C0B9B007}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{EA109011-75D6-4B4C-8940-30E2C0B9B007}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="111">
   <si>
     <t>Problem</t>
   </si>
@@ -345,6 +345,77 @@
 4. Problem involves comparing elements from both ends
 5. Two indices move through the array to reduce search space.
 6. In-place Modification is being asked</t>
+  </si>
+  <si>
+    <t>Trigger : Sorted array and comparison of positions</t>
+  </si>
+  <si>
+    <t>Result array is filled from the back because we are placing the largest square first
+i &lt; j is not the right loop condition here — use index &gt;= 0 to ensure all positions are filled</t>
+  </si>
+  <si>
+    <t>Array can be sorted and I could use Two Sum Approach</t>
+  </si>
+  <si>
+    <t>We just hold one element of array and apply Two Sum approach on it.</t>
+  </si>
+  <si>
+    <t>Make sure to handle the duplicates condition if asked in the question</t>
+  </si>
+  <si>
+    <t>O(n²)</t>
+  </si>
+  <si>
+    <t>Array | List&lt;List&gt;</t>
+  </si>
+  <si>
+    <t>Minimum Size Subarray Sum</t>
+  </si>
+  <si>
+    <t>Video</t>
+  </si>
+  <si>
+    <t>Subarray + minimum length -&gt; Dynamic Sliding Window</t>
+  </si>
+  <si>
+    <t>Dynamic Window</t>
+  </si>
+  <si>
+    <t>Even though there's a nested while loop, it's not O(n²) because low never resets — it only moves forward.</t>
+  </si>
+  <si>
+    <t>Use inner while loop not if — keep shrinking the window as long as sum &gt;= target to find minimum</t>
+  </si>
+  <si>
+    <t>Largest squares are always at either end. Use opposite end pointers, fill result array from right to left.
+In-place modification doesn't work because overwriting loses original values needed for comparison</t>
+  </si>
+  <si>
+    <t>Longest Substring with K Uniques</t>
+  </si>
+  <si>
+    <t>Longest Substring with At Least K Repeating Characters</t>
+  </si>
+  <si>
+    <t>Input is a string + find longest substring + constraint on K unique elements inside window → Dynamic Sliding Window</t>
+  </si>
+  <si>
+    <t>Array | Map</t>
+  </si>
+  <si>
+    <t>Shrink window from left when map.size() &gt; k — not when duplicates appear
+Decrement frequency first, then check if it became 0 before removing from map
+map.size() == k is the only valid state to update result</t>
+  </si>
+  <si>
+    <t>map.size() &lt; k → just expand, no action needed
+map.size() &gt; k → shrink from left until map size is back to k
+Return -1 as default result handles the case where no valid substring exists
+getOrDefault(ch, 0) + 1 — if character exists return its count, else return 0, then increment</t>
+  </si>
+  <si>
+    <t>O(k+1)
+since the map holds at most k+1 distinct characters at any point.</t>
   </si>
 </sst>
 </file>
@@ -405,7 +476,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -436,8 +507,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -452,19 +529,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -513,18 +577,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -536,6 +588,18 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -971,82 +1035,82 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="142.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="171.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="15" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1066,11 +1130,13 @@
     <col min="1" max="1" width="31.21875" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.88671875" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" customWidth="1"/>
     <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.21875" customWidth="1"/>
-    <col min="8" max="11" width="25.88671875" customWidth="1"/>
+    <col min="8" max="9" width="25.88671875" customWidth="1"/>
+    <col min="10" max="10" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="15.33203125" customWidth="1"/>
     <col min="14" max="14" width="15.44140625" customWidth="1"/>
@@ -1218,55 +1284,91 @@
       <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="C4" s="2">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="1"/>
+      <c r="F4" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M4" s="18">
+        <v>46089</v>
+      </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="C5" s="2">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M5" s="1"/>
+        <v>96</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M5" s="18">
+        <v>46091</v>
+      </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -1657,15 +1759,15 @@
   <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.33203125" customWidth="1"/>
     <col min="2" max="2" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.44140625" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36.44140625" customWidth="1"/>
     <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.21875" customWidth="1"/>
-    <col min="9" max="9" width="23" customWidth="1"/>
+    <col min="8" max="8" width="39.44140625" customWidth="1"/>
+    <col min="9" max="9" width="31.6640625" customWidth="1"/>
     <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.21875" bestFit="1" customWidth="1"/>
@@ -1725,7 +1827,7 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="10" t="s">
         <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1768,7 +1870,7 @@
       <c r="Q2" s="7"/>
     </row>
     <row r="3" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="20" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1783,7 +1885,7 @@
       <c r="E3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="13" t="s">
         <v>73</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -1811,7 +1913,7 @@
       <c r="Q3" s="9"/>
     </row>
     <row r="4" spans="1:17" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="20" t="s">
         <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1826,7 +1928,7 @@
       <c r="E4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="13" t="s">
         <v>73</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -1853,56 +1955,108 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1"/>
+    <row r="5" spans="1:17" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="2">
+        <v>30</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1"/>
+    <row r="6" spans="1:17" ht="144" x14ac:dyDescent="0.3">
+      <c r="A6" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="2">
+        <v>40</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
+    <row r="7" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -1911,17 +2065,17 @@
       <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -1930,17 +2084,17 @@
       <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -1949,17 +2103,17 @@
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -1968,17 +2122,17 @@
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -1987,17 +2141,17 @@
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -2006,17 +2160,17 @@
       <c r="Q12" s="1"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -2026,16 +2180,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -2044,17 +2198,17 @@
       <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -2063,17 +2217,17 @@
       <c r="Q15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -2083,16 +2237,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -2101,12 +2255,12 @@
       <c r="Q17" s="1"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -2120,12 +2274,12 @@
       <c r="Q18" s="1"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -2139,12 +2293,12 @@
       <c r="Q19" s="1"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -2158,12 +2312,12 @@
       <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -2177,12 +2331,12 @@
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -2200,8 +2354,11 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{F0E6F405-EB37-4CA7-A358-5C666F410C53}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{2BCB52B1-9CB6-494C-9F8E-890F1DD4D441}"/>
     <hyperlink ref="A4" r:id="rId3" display="https://leetcode.com/problems/maximum-sum-of-distinct-subarrays-with-length-k/" xr:uid="{4CDD9DB7-8216-4628-895A-252CDC46323E}"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://leetcode.com/problems/minimum-size-subarray-sum/" xr:uid="{87D89978-DEC6-4FE3-9F53-3AFE52A15A93}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{4DBED0AB-BA0A-4904-AE72-1D2F538572E8}"/>
+    <hyperlink ref="A7" r:id="rId6" display="https://leetcode.com/problems/longest-substring-with-at-least-k-repeating-characters/" xr:uid="{5A07E760-C3F5-431C-ADA6-C6958C0C4F79}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId7"/>
 </worksheet>
 </file>
--- a/DSA Tracking Sheet.xlsx
+++ b/DSA Tracking Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Structures and Algorithm\Pattern_Based_DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185BF15C-A265-4E82-96D3-ABD93FF48AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DAC298-4FC1-4973-91BE-EF2A8206A856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{EA109011-75D6-4B4C-8940-30E2C0B9B007}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="130">
   <si>
     <t>Problem</t>
   </si>
@@ -416,6 +416,78 @@
   <si>
     <t>O(k+1)
 since the map holds at most k+1 distinct characters at any point.</t>
+  </si>
+  <si>
+    <t>Fruit Into Baskets</t>
+  </si>
+  <si>
+    <t>O(1)
+The map holds at most 3 entries at any point — you remove when size exceeds 2. So space is O(1) (or O(k) where k=2, which is constant)</t>
+  </si>
+  <si>
+    <t>Two baskets = at most 2 distinct values → Dynamic Sliding Window + HashMap
+This is identical to Longest K Distinct Characters with k=2
+Shrink window from left when map.size() &gt; 2, update result when map.size() &lt;= 2</t>
+  </si>
+  <si>
+    <t>Initialize maxLength with Integer.MIN_VALUE — but be careful, if all windows have less than 2 distinct types, == 2 condition never triggers. Use &lt;= 2 to handle arrays with only 1 distinct fruit type</t>
+  </si>
+  <si>
+    <t>input is an array + find the longest subarray with at most 2 distinct number</t>
+  </si>
+  <si>
+    <t>Longest Substring Without Repeating Characters</t>
+  </si>
+  <si>
+    <t>input is an array + find the longest subarray with unique characters</t>
+  </si>
+  <si>
+    <t>Window becomes invalid when any character's frequency &gt; 1, not when map.size() exceeds something
+Use while not if for shrinking — if only removes one character from left, but the duplicate may not be at low
+Update maxLen after every shrink — at that point window is guaranteed valid</t>
+  </si>
+  <si>
+    <t>Space is O(1) not O(n) — map is bounded by character set size (26 for lowercase, 128 for ASCII)
+Key difference from previous problems: invalid condition is frequency based, not map size based
+Shrink continues until the duplicate character is actually removed from the window</t>
+  </si>
+  <si>
+    <t>Longest Repeating Character Replacement</t>
+  </si>
+  <si>
+    <t>Hard</t>
+  </si>
+  <si>
+    <t>input is string + find the longest substring with a condition</t>
+  </si>
+  <si>
+    <t>Space is O(1) — map bounded by 26 uppercase characters, not input size
+Use while not if for shrinking — window may need multiple shrinks before becoming valid
+You don't actually perform replacements — you just check if it's feasible within k operations</t>
+  </si>
+  <si>
+    <t>Minimum Window Substring</t>
+  </si>
+  <si>
+    <t>AI + Video</t>
+  </si>
+  <si>
+    <t>input is string + find the shortest substring with a condition</t>
+  </si>
+  <si>
+    <t>Use required counter starting at t.length() — decrements when windowFreq &lt;= tFreq for a needed char, increments when shrinking drops a char below required frequency
+Window is valid when required == 0
+Record window only when current length &lt; minLen — not on every valid window
+Use s.substring(low, high + 1) not s.substring(low, low + minLen) — minLen may be from a previous smaller window</t>
+  </si>
+  <si>
+    <t>windowFreq &lt;= tFreq condition handles duplicates — for t = "aaa", required decrements 3 times as a frequency grows from 1 to 3
+During shrink, required++ only when tMap.containsKey(char) AND windowFreq drops below tFreq — not just when frequency hits 0
+This is harder than it looks — the required counter is the key insight that avoids comparing two full maps at every step
+Space O(1) — both maps bounded by 52 characters (26 uppercase + 26 lowercase)</t>
+  </si>
+  <si>
+    <t>O(m+n)</t>
   </si>
 </sst>
 </file>
@@ -542,7 +614,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -592,14 +664,23 @@
     <xf numFmtId="15" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1035,15 +1116,15 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
     </row>
     <row r="6" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="14" t="s">
@@ -1869,8 +1950,8 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
     </row>
-    <row r="3" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+    <row r="3" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1912,8 +1993,8 @@
       <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+    <row r="4" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
         <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1955,8 +2036,8 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:17" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="19" t="s">
         <v>97</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1999,7 +2080,7 @@
       <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="1:17" ht="144" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>104</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -2042,7 +2123,7 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="20" t="s">
         <v>105</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -2055,8 +2136,6 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -2064,76 +2143,172 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="20"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
+    <row r="8" spans="1:17" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="2">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
+    <row r="9" spans="1:17" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="2">
+        <v>30</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="20"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
+    <row r="10" spans="1:17" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="2">
+        <v>50</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="20"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+    <row r="11" spans="1:17" ht="216" x14ac:dyDescent="0.3">
+      <c r="A11" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="2">
+        <v>70</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -2141,7 +2316,7 @@
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="20"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -2160,7 +2335,7 @@
       <c r="Q12" s="1"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
+      <c r="A13" s="19"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -2198,7 +2373,7 @@
       <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="20"/>
+      <c r="A15" s="19"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -2217,7 +2392,7 @@
       <c r="Q15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="20"/>
+      <c r="A16" s="19"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2255,7 +2430,7 @@
       <c r="Q17" s="1"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="20"/>
+      <c r="A18" s="19"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -2274,7 +2449,7 @@
       <c r="Q18" s="1"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="20"/>
+      <c r="A19" s="19"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -2293,7 +2468,7 @@
       <c r="Q19" s="1"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="20"/>
+      <c r="A20" s="19"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -2312,7 +2487,7 @@
       <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="20"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -2331,7 +2506,7 @@
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="20"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -2357,8 +2532,12 @@
     <hyperlink ref="A5" r:id="rId4" display="https://leetcode.com/problems/minimum-size-subarray-sum/" xr:uid="{87D89978-DEC6-4FE3-9F53-3AFE52A15A93}"/>
     <hyperlink ref="A6" r:id="rId5" xr:uid="{4DBED0AB-BA0A-4904-AE72-1D2F538572E8}"/>
     <hyperlink ref="A7" r:id="rId6" display="https://leetcode.com/problems/longest-substring-with-at-least-k-repeating-characters/" xr:uid="{5A07E760-C3F5-431C-ADA6-C6958C0C4F79}"/>
+    <hyperlink ref="A8" r:id="rId7" display="https://leetcode.com/problems/fruit-into-baskets/" xr:uid="{F73B731F-FF91-4C17-A873-E2F13B1BF745}"/>
+    <hyperlink ref="A9" r:id="rId8" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/" xr:uid="{77937BF3-2DD6-4846-8E8D-B36466EE3597}"/>
+    <hyperlink ref="A10" r:id="rId9" display="https://leetcode.com/problems/longest-repeating-character-replacement/" xr:uid="{0D5423E5-349D-410E-BA09-77EF8855B792}"/>
+    <hyperlink ref="A11" r:id="rId10" display="https://leetcode.com/problems/minimum-window-substring/" xr:uid="{2CFF3C27-EA43-4238-8246-53038B73E0F3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId7"/>
+  <drawing r:id="rId11"/>
 </worksheet>
 </file>
--- a/DSA Tracking Sheet.xlsx
+++ b/DSA Tracking Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Structures and Algorithm\Pattern_Based_DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DAC298-4FC1-4973-91BE-EF2A8206A856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F0EC1A-193B-4A0E-ACBC-A8ADC01A0CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{EA109011-75D6-4B4C-8940-30E2C0B9B007}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{EA109011-75D6-4B4C-8940-30E2C0B9B007}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="150">
   <si>
     <t>Problem</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>Two Sum II - Input Array Is Sorted</t>
-  </si>
-  <si>
-    <t>Done</t>
   </si>
   <si>
     <t>Segregate 0s and 1s</t>
@@ -475,19 +472,107 @@
     <t>input is string + find the shortest substring with a condition</t>
   </si>
   <si>
-    <t>Use required counter starting at t.length() — decrements when windowFreq &lt;= tFreq for a needed char, increments when shrinking drops a char below required frequency
-Window is valid when required == 0
-Record window only when current length &lt; minLen — not on every valid window
-Use s.substring(low, high + 1) not s.substring(low, low + minLen) — minLen may be from a previous smaller window</t>
-  </si>
-  <si>
-    <t>windowFreq &lt;= tFreq condition handles duplicates — for t = "aaa", required decrements 3 times as a frequency grows from 1 to 3
-During shrink, required++ only when tMap.containsKey(char) AND windowFreq drops below tFreq — not just when frequency hits 0
-This is harder than it looks — the required counter is the key insight that avoids comparing two full maps at every step
-Space O(1) — both maps bounded by 52 characters (26 uppercase + 26 lowercase)</t>
-  </si>
-  <si>
     <t>O(m+n)</t>
+  </si>
+  <si>
+    <t>needed = number of unique characters in t (tMap.size()), have = unique characters fully satisfied in window
+Window valid when have == needed — cleaner than required == 0 because duplicates handled implicitly by frequency check
+Use .equals() not == for Integer comparison in map — == compares object references, not values
+Store result as int[] {start, end} indices — reconstruct string at the end, not inside the loop</t>
+  </si>
+  <si>
+    <t>Key difference from previous approach: needed tracks unique chars not total chars, so have only increments when frequency exactly matches tMap
+have decrements only when frequency drops below tMap requirement during shrink</t>
+  </si>
+  <si>
+    <t>Input is array + find all subarrays with a condition</t>
+  </si>
+  <si>
+    <t>When window is valid (product &lt; k), number of new subarrays ending at high is exactly high - low + 1
+Shrink with while not if — product may still be &gt;= k after removing one element
+Use low &lt;= high not low &lt; n — prevents empty/invalid window from adding wrong count</t>
+  </si>
+  <si>
+    <t>Count subarrays after the while loop, not inside it — avoids double counting
+product /= nums[low] to shrink — division undoes the multiplication when element leaves
+If k &lt;= 1, no subarray can have product less than k (all elements &gt;= 1), result is 0 — consider this edge case
+Space O(1) — only tracking product, low, and count</t>
+  </si>
+  <si>
+    <t>Palindromic Substrings</t>
+  </si>
+  <si>
+    <t>Track closestSum using Math.abs(sum - target) &lt; Math.abs(closestSum - target) — whoever has smaller distance wins
+Initialize closestSum with first three elements sum, not Integer.MAX_VALUE — MAX_VALUE causes overflow in Math.abs(closestSum - target)
+Early return if sum == target — can't get closer than exact match</t>
+  </si>
+  <si>
+    <t>Sort is required — without it two pointers can't eliminate search space
+Make sure to frequently revise this</t>
+  </si>
+  <si>
+    <t>Sorted array + count triplets with sum &lt; target → Sort + Fixed pointer + Two Pointers
+When nums[i] + nums[left] + nums[right] &lt; target, all positions of right between left+1 and current right are also valid — add right - left to count, not just 1
+When sum &gt;= target, move right left to decrease sum
+When sum &lt; target, add right - left and move left right</t>
+  </si>
+  <si>
+    <t>triplets += right - left only inside the valid condition (currentSum &lt; sum) — runs unconditionally is a bug</t>
+  </si>
+  <si>
+    <t>Solution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Input is array + in-place modification required + maintain relative order → Same Direction Two Pointers</t>
+  </si>
+  <si>
+    <t>Same Direction</t>
+  </si>
+  <si>
+    <t>i tracks the position where the next non-zero element should be placed
+j scans every element — when it finds a non-zero, swap with nums[i] and advance i
+Opposite end pointers don't work here — swapping from both ends breaks relative order
+j always moves forward, i only moves when a non-zero is placed</t>
+  </si>
+  <si>
+    <t>No edge case needed — single loop handles arrays of any size including single element
+After loop ends, all non-zeros are at the front in original order, zeros naturally fall to the end</t>
+  </si>
+  <si>
+    <t>Sort 0s, 1s and 2s</t>
+  </si>
+  <si>
+    <t>Input is array + in-place sorting without built-in sort + only 3 distinct values → Two/Three Pointers (Dutch National Flag)</t>
+  </si>
+  <si>
+    <t>Three pointers</t>
+  </si>
+  <si>
+    <t>Three pointers: low tracks boundary for 0s, mid scans current element, high tracks boundary for 2s
+When arr[mid] == 0 → swap with low, move both low and mid forward
+When arr[mid] == 1 → just move mid forward, 1s naturally fall in the middle
+When arr[mid] == 2 → swap with high, move high backward but not mid — swapped element from high is unknown and needs to be checked
+Loop ends when mid &gt; high — everything beyond high is already sorted as 2s</t>
+  </si>
+  <si>
+    <t>Brute force: count 0s, 1s, 2s then overwrite array — O(n) time O(1) space but two passes
+Dutch National Flag: single pass O(n) time O(1) space
+Key difference from Move Zeroes — here we need 3 pointers because we have 3 categories not 2
+Don't increment mid when swapping with high — the incoming element from high is unverified</t>
+  </si>
+  <si>
+    <t>input is array + compute trapped water + involves comparing elements from both ends + min of two walls determines water level at each position</t>
+  </si>
+  <si>
+    <t>Water at any index = min(leftMax, rightMax) - height[i]
+leftMax and rightMax must include height[i] itself — ensures result never goes negative
+If leftMax &lt; rightMax, leftMax is the bottleneck — no need to know exact rightMax, process from left
+If rightMax &lt;= leftMax, rightMax is the bottleneck — process from right
+Move the pointer of the smaller max inward — update max before calculating water</t>
+  </si>
+  <si>
+    <t>In two pointers — move pointer first, then update max, then calculate water. Order matters.</t>
   </si>
 </sst>
 </file>
@@ -548,7 +633,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -585,8 +670,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -609,12 +712,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -676,11 +792,40 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -712,8 +857,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>304800</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1116,34 +1261,34 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="B5" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
+      <c r="B5" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
     </row>
     <row r="6" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="D6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>40</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>41</v>
       </c>
       <c r="H6" s="14" t="s">
         <v>1</v>
@@ -1151,48 +1296,48 @@
     </row>
     <row r="7" spans="2:8" ht="142.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="G7" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="171.6" x14ac:dyDescent="0.3">
       <c r="B8" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="16" t="s">
+      <c r="H8" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1208,14 +1353,15 @@
   <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.21875" customWidth="1"/>
+    <col min="1" max="1" width="32.88671875" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.33203125" customWidth="1"/>
     <col min="4" max="4" width="7.88671875" customWidth="1"/>
     <col min="5" max="5" width="19.5546875" customWidth="1"/>
     <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.21875" customWidth="1"/>
-    <col min="8" max="9" width="25.88671875" customWidth="1"/>
+    <col min="8" max="8" width="37.44140625" customWidth="1"/>
+    <col min="9" max="9" width="25.88671875" customWidth="1"/>
     <col min="10" max="10" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
@@ -1231,34 +1377,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>1</v>
@@ -1279,128 +1425,128 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="5" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:17" s="5" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2">
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" s="13" t="s">
+      <c r="J2" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+    </row>
+    <row r="3" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-    </row>
-    <row r="3" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="C3" s="2">
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F3" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G3" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>87</v>
-      </c>
       <c r="J3" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="K3" s="13" t="s">
-        <v>81</v>
-      </c>
       <c r="L3" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-    </row>
-    <row r="4" spans="1:17" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>11</v>
+        <v>84</v>
+      </c>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+    </row>
+    <row r="4" spans="1:17" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="2">
         <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="G4" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="J4" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M4" s="18">
         <v>46089</v>
@@ -1411,41 +1557,41 @@
       <c r="Q4" s="1"/>
     </row>
     <row r="5" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>12</v>
+      <c r="A5" s="25" t="s">
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F5" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="J5" s="13" t="s">
-        <v>95</v>
-      </c>
       <c r="K5" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M5" s="18">
         <v>46091</v>
@@ -1455,91 +1601,155 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+    <row r="6" spans="1:17" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="2">
+        <v>50</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>81</v>
+      </c>
       <c r="E6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M6" s="18">
+        <v>46096</v>
+      </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+    <row r="7" spans="1:17" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="2">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M7" s="18">
+        <v>46096</v>
+      </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+    <row r="8" spans="1:17" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="2">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M8" s="18">
+        <v>46102</v>
+      </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>18</v>
+      <c r="A9" s="25" t="s">
+        <v>17</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="1"/>
       <c r="I9" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
@@ -1551,14 +1761,14 @@
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>20</v>
+      <c r="A10" s="25" t="s">
+        <v>19</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="1"/>
@@ -1574,8 +1784,8 @@
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>22</v>
+      <c r="A11" s="25" t="s">
+        <v>21</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1595,8 +1805,8 @@
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>23</v>
+      <c r="A12" s="25" t="s">
+        <v>22</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1616,8 +1826,8 @@
       <c r="Q12" s="1"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>24</v>
+      <c r="A13" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1637,8 +1847,8 @@
       <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
-        <v>25</v>
+      <c r="A14" s="25" t="s">
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1658,8 +1868,8 @@
       <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
-        <v>26</v>
+      <c r="A15" s="25" t="s">
+        <v>25</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1679,8 +1889,8 @@
       <c r="Q15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>27</v>
+      <c r="A16" s="25" t="s">
+        <v>26</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1699,9 +1909,9 @@
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
-        <v>28</v>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" s="25" t="s">
+        <v>27</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1720,42 +1930,86 @@
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
+    <row r="18" spans="1:17" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="2">
+        <v>75</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+    <row r="19" spans="1:17" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="2">
+        <v>60</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="I19" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -1763,14 +2017,22 @@
       <c r="Q19" s="1"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
+      <c r="A20" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="2">
+        <v>5</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1784,8 +2046,8 @@
       <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
-        <v>32</v>
+      <c r="A21" s="25" t="s">
+        <v>31</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1814,20 +2076,20 @@
     <hyperlink ref="A5" r:id="rId4" display="https://leetcode.com/problems/3sum/" xr:uid="{45F2F3B9-6231-49FC-875F-A2AE1CC5391D}"/>
     <hyperlink ref="A6" r:id="rId5" display="https://leetcode.com/problems/3sum-closest/" xr:uid="{1E5D4D8B-9872-44F7-BE8B-27DD24FE696D}"/>
     <hyperlink ref="A7" r:id="rId6" xr:uid="{E75482B9-8D8E-49D3-A11C-B7E65BDE6775}"/>
-    <hyperlink ref="A8" r:id="rId7" display="https://leetcode.com/problems/subarray-product-less-than-k/" xr:uid="{763B5E98-D01B-47F8-BC4E-F104AD50B360}"/>
-    <hyperlink ref="A9" r:id="rId8" display="https://leetcode.com/problems/sort-colors/" xr:uid="{66835CC3-56DF-48A5-A227-C77DB4477FE1}"/>
-    <hyperlink ref="A10" r:id="rId9" display="https://leetcode.com/problems/backspace-string-compare/" xr:uid="{A6FC8A45-5B49-4A8D-8E1A-5C30EAC03D95}"/>
-    <hyperlink ref="A11" r:id="rId10" xr:uid="{F96FFF5E-5DA9-488B-B6BF-E7B3A29950B7}"/>
-    <hyperlink ref="A12" r:id="rId11" xr:uid="{83B969A3-5555-4ED7-ACCC-BC52B0CEA4F0}"/>
-    <hyperlink ref="A13" r:id="rId12" display="https://leetcode.com/problems/container-with-most-water/" xr:uid="{02946851-91DF-4517-9D35-5CBA4F9B36FA}"/>
-    <hyperlink ref="A14" r:id="rId13" display="https://leetcode.com/problems/find-all-duplicates-in-an-array/" xr:uid="{F3F491DD-C76C-4779-8AFB-4B80D46253AC}"/>
-    <hyperlink ref="A15" r:id="rId14" display="https://leetcode.com/problems/merge-sorted-array/" xr:uid="{E3FA6623-EF03-4012-92F2-24CA05E33416}"/>
-    <hyperlink ref="A16" r:id="rId15" xr:uid="{08B767B9-CF56-471C-AF7A-84DA7FF9D017}"/>
-    <hyperlink ref="A17" r:id="rId16" display="https://leetcode.com/problems/remove-duplicates-from-sorted-array/" xr:uid="{68CEAAD9-5603-46FC-97FE-378533FFE3B0}"/>
-    <hyperlink ref="A18" r:id="rId17" display="https://leetcode.com/problems/trapping-rain-water/" xr:uid="{B9927F6B-CBDA-486F-A27E-024253D5389E}"/>
-    <hyperlink ref="A19" r:id="rId18" display="https://leetcode.com/problems/move-zeroes/" xr:uid="{35A79DBB-00D5-4C74-BC90-782FC035EA7B}"/>
-    <hyperlink ref="A20" r:id="rId19" display="https://leetcode.com/problems/reverse-string/" xr:uid="{D88BB189-E81E-411F-8551-B4FAB70D208B}"/>
-    <hyperlink ref="A21" r:id="rId20" display="https://leetcode.com/problems/valid-palindrome-ii/" xr:uid="{D6F9D2FC-C252-48B2-8806-1529AC8AC8B6}"/>
+    <hyperlink ref="A9" r:id="rId7" display="https://leetcode.com/problems/sort-colors/" xr:uid="{66835CC3-56DF-48A5-A227-C77DB4477FE1}"/>
+    <hyperlink ref="A10" r:id="rId8" display="https://leetcode.com/problems/backspace-string-compare/" xr:uid="{A6FC8A45-5B49-4A8D-8E1A-5C30EAC03D95}"/>
+    <hyperlink ref="A11" r:id="rId9" xr:uid="{F96FFF5E-5DA9-488B-B6BF-E7B3A29950B7}"/>
+    <hyperlink ref="A12" r:id="rId10" xr:uid="{83B969A3-5555-4ED7-ACCC-BC52B0CEA4F0}"/>
+    <hyperlink ref="A13" r:id="rId11" display="https://leetcode.com/problems/container-with-most-water/" xr:uid="{02946851-91DF-4517-9D35-5CBA4F9B36FA}"/>
+    <hyperlink ref="A14" r:id="rId12" display="https://leetcode.com/problems/find-all-duplicates-in-an-array/" xr:uid="{F3F491DD-C76C-4779-8AFB-4B80D46253AC}"/>
+    <hyperlink ref="A15" r:id="rId13" display="https://leetcode.com/problems/merge-sorted-array/" xr:uid="{E3FA6623-EF03-4012-92F2-24CA05E33416}"/>
+    <hyperlink ref="A16" r:id="rId14" xr:uid="{08B767B9-CF56-471C-AF7A-84DA7FF9D017}"/>
+    <hyperlink ref="A17" r:id="rId15" display="https://leetcode.com/problems/remove-duplicates-from-sorted-array/" xr:uid="{68CEAAD9-5603-46FC-97FE-378533FFE3B0}"/>
+    <hyperlink ref="A18" r:id="rId16" display="https://leetcode.com/problems/trapping-rain-water/" xr:uid="{B9927F6B-CBDA-486F-A27E-024253D5389E}"/>
+    <hyperlink ref="A19" r:id="rId17" display="https://leetcode.com/problems/move-zeroes/" xr:uid="{35A79DBB-00D5-4C74-BC90-782FC035EA7B}"/>
+    <hyperlink ref="A20" r:id="rId18" display="https://leetcode.com/problems/reverse-string/" xr:uid="{D88BB189-E81E-411F-8551-B4FAB70D208B}"/>
+    <hyperlink ref="A21" r:id="rId19" display="https://leetcode.com/problems/valid-palindrome-ii/" xr:uid="{D6F9D2FC-C252-48B2-8806-1529AC8AC8B6}"/>
+    <hyperlink ref="A8" r:id="rId20" xr:uid="{00A8B67A-AC73-4BA2-80C1-E76CE76D55C9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId21"/>
@@ -1859,34 +2121,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>1</v>
@@ -1909,40 +2171,40 @@
     </row>
     <row r="2" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2">
         <v>60</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="I2" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J2" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="K2" s="13" t="s">
-        <v>81</v>
-      </c>
       <c r="L2" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -1952,40 +2214,40 @@
     </row>
     <row r="3" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2">
         <v>120</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H3" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="I3" s="11" t="s">
-        <v>76</v>
-      </c>
       <c r="J3" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
@@ -1995,40 +2257,40 @@
     </row>
     <row r="4" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2">
         <v>120</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -2038,40 +2300,40 @@
     </row>
     <row r="5" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="13" t="s">
+      <c r="G5" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="H5" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>101</v>
-      </c>
       <c r="J5" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K5" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="K5" s="13" t="s">
-        <v>81</v>
-      </c>
       <c r="L5" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -2081,40 +2343,40 @@
     </row>
     <row r="6" spans="1:17" ht="144" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" s="2">
         <v>40</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="H6" s="11" t="s">
+      <c r="I6" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="J6" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="J6" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>110</v>
-      </c>
       <c r="L6" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -2124,10 +2386,10 @@
     </row>
     <row r="7" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -2145,40 +2407,40 @@
     </row>
     <row r="8" spans="1:17" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A8" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2">
         <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H8" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="I8" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="I8" s="11" t="s">
-        <v>114</v>
-      </c>
       <c r="J8" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -2188,40 +2450,40 @@
     </row>
     <row r="9" spans="1:17" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="2">
         <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F9" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G9" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="H9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="J9" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="L9" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -2231,40 +2493,40 @@
     </row>
     <row r="10" spans="1:17" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A10" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="C10" s="2">
         <v>50</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F10" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="G10" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>123</v>
-      </c>
       <c r="J10" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="L10" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -2272,42 +2534,42 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:17" ht="216" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
-        <v>124</v>
+    <row r="11" spans="1:17" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="23" t="s">
+        <v>123</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2">
         <v>70</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F11" s="13" t="s">
+      <c r="G11" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="J11" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="G11" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>129</v>
-      </c>
       <c r="K11" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -2315,19 +2577,43 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="19"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
+    <row r="12" spans="1:17" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="2">
+        <v>50</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -2335,8 +2621,12 @@
       <c r="Q12" s="1"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="1"/>
+      <c r="A13" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -2536,8 +2826,10 @@
     <hyperlink ref="A9" r:id="rId8" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/" xr:uid="{77937BF3-2DD6-4846-8E8D-B36466EE3597}"/>
     <hyperlink ref="A10" r:id="rId9" display="https://leetcode.com/problems/longest-repeating-character-replacement/" xr:uid="{0D5423E5-349D-410E-BA09-77EF8855B792}"/>
     <hyperlink ref="A11" r:id="rId10" display="https://leetcode.com/problems/minimum-window-substring/" xr:uid="{2CFF3C27-EA43-4238-8246-53038B73E0F3}"/>
+    <hyperlink ref="A12" r:id="rId11" display="https://leetcode.com/problems/subarray-product-less-than-k/" xr:uid="{8A1874FB-60C6-4633-AD8D-B0FF2482F64A}"/>
+    <hyperlink ref="A13" r:id="rId12" display="https://leetcode.com/problems/palindromic-substrings/" xr:uid="{AF3B70E2-357B-4ECA-AE9F-892D5E407345}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId11"/>
+  <drawing r:id="rId13"/>
 </worksheet>
 </file>
--- a/DSA Tracking Sheet.xlsx
+++ b/DSA Tracking Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Structures and Algorithm\Pattern_Based_DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F0EC1A-193B-4A0E-ACBC-A8ADC01A0CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AAAEC8C-20E7-4193-99CE-309D9E825D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{EA109011-75D6-4B4C-8940-30E2C0B9B007}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="157">
   <si>
     <t>Problem</t>
   </si>
@@ -573,6 +573,40 @@
   </si>
   <si>
     <t>In two pointers — move pointer first, then update max, then calculate water. Order matters.</t>
+  </si>
+  <si>
+    <t>Input is a string + check if it reads same forward and backward + contains non-alphanumeric characters that need to be ignored → Opposite End Two Pointers</t>
+  </si>
+  <si>
+    <t>Convert to lowercase first before any comparison — handles case insensitivity
+Skip non-alphanumeric characters using inner while loops with Character.isLetterOrDigit()
+Inner while loops must have l&lt;r condition — prevents pointers from crossing and avoids wrong comparisons
+No need to create a cleaned string separately — skip invalid characters in-place using pointers
+Empty string after cleaning is a valid palindrome — outer while loop handles this naturally</t>
+  </si>
+  <si>
+    <t>no extra string created, pointers work directly on original string
+Time O(n) — each character visited at most once
+Common mistake — forgetting l&lt;r inside inner while loops causes pointers to cross or IndexOutOfBoundsException
+Character.isLetterOrDigit() handles both letters and digits — no need to write custom checks</t>
+  </si>
+  <si>
+    <t>Opposite End (both pointers move right to left)</t>
+  </si>
+  <si>
+    <t>Process right to left — seeing # tells you the next valid character to the left must be skipped
+Use a skip counter — increment on #, decrement and skip when a valid character is found with skip &gt; 0
+Use nested while loops to fully exhaust all skips before comparing — do not compare until both pointers are on a valid character
+If one pointer has valid characters remaining and the other is exhausted → return false immediately
+Brute force uses two Stacks — push on valid character, pop on #, compare stacks at end → O(n) time O(n) space
+Two pointers → O(n) time O(1) space</t>
+  </si>
+  <si>
+    <t>Most common mistake — using if blocks instead of nested while loops, causes incorrect skipping
+Always add bounds check i &gt;= 0 before calling charAt(i) — pointer can go to -1 after decrementing</t>
+  </si>
+  <si>
+    <t>Input is two strings + special character affects previous character + compare final result of both strings → Two Pointers from the end + skip counter</t>
   </si>
 </sst>
 </file>
@@ -730,7 +764,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -818,14 +852,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1261,15 +1298,15 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="14" t="s">
@@ -1350,7 +1387,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5DFE80-2C44-488B-9D8D-62ACD873F97E}">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.88671875" customWidth="1"/>
@@ -1707,13 +1744,13 @@
       <c r="E8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="34" t="s">
         <v>143</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="H8" s="34" t="s">
+      <c r="H8" s="33" t="s">
         <v>145</v>
       </c>
       <c r="I8" s="11" t="s">
@@ -1804,21 +1841,43 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="1"/>
+      <c r="B12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="2">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -1946,7 +2005,7 @@
       <c r="E18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="35" t="s">
+      <c r="F18" s="34" t="s">
         <v>147</v>
       </c>
       <c r="G18" s="13" t="s">
@@ -2065,6 +2124,49 @@
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
+    </row>
+    <row r="22" spans="1:17" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="2">
+        <v>120</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q1" xr:uid="{DF5DFE80-2C44-488B-9D8D-62ACD873F97E}"/>
@@ -2090,10 +2192,11 @@
     <hyperlink ref="A20" r:id="rId18" display="https://leetcode.com/problems/reverse-string/" xr:uid="{D88BB189-E81E-411F-8551-B4FAB70D208B}"/>
     <hyperlink ref="A21" r:id="rId19" display="https://leetcode.com/problems/valid-palindrome-ii/" xr:uid="{D6F9D2FC-C252-48B2-8806-1529AC8AC8B6}"/>
     <hyperlink ref="A8" r:id="rId20" xr:uid="{00A8B67A-AC73-4BA2-80C1-E76CE76D55C9}"/>
+    <hyperlink ref="A22" r:id="rId21" display="https://leetcode.com/problems/backspace-string-compare/" xr:uid="{73BA1C93-1169-41A4-9666-9F8802B8C1A2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId21"/>
-  <drawing r:id="rId22"/>
+  <pageSetup orientation="portrait" r:id="rId22"/>
+  <drawing r:id="rId23"/>
 </worksheet>
 </file>
 
